--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>821400</v>
+      </c>
+      <c r="E8" s="3">
         <v>477100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>675100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>250200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>301100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>429900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>416600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>257500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>255900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>252200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>237200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>220600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>155400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>123000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>138000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>70200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>552400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E9" s="3">
         <v>100200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>206400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>102900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>109800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>115500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>104500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>93600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>87200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>87500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>83000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>86800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>51700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>290700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>818200</v>
+      </c>
+      <c r="E10" s="3">
         <v>376900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>468700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>147300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>191300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>314400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>312100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>163900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>168700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>103700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>81000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>98300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>261700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,120 +1061,129 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>133400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>43300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1426800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>471900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E15" s="3">
         <v>128000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>291100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>141600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>147400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>145600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>155400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>128600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>132900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>129200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>138200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>139400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>85600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>80600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>74800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>38100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>110100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>551900</v>
+      </c>
+      <c r="E17" s="3">
         <v>195800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>997400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>527200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>306900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>468400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>483400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>501200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>280400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>304100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>308600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>390100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>241100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>624600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>161900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1036000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>269500</v>
+      </c>
+      <c r="E18" s="3">
         <v>281300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-322300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-277000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-38500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-66800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-243700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-51900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-71400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-169500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-85700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-65900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-486600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-91700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-483600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,13 +1342,14 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>96100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1358,72 +1391,78 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>851200</v>
+      </c>
+      <c r="E21" s="3">
         <v>409200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-31200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-135500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>141500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>107100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>88500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-112800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>113500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>86200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>98700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>53100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>100600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-213600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-364300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,120 +1517,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>365600</v>
+      </c>
+      <c r="E23" s="3">
         <v>281200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-322400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-277100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-66800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-243700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-51900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-71400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-169500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-85700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-65900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-486600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-91800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-483700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>31200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-11000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-75200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-23200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-18700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-15100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>281400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-326700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-278100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-64300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-236300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-146300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-67000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-471500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-86500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-483900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>241900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-336400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-197800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-49500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-169200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-104300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-42400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-432200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-83200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-453100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,64 +1871,70 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-320500</v>
+      </c>
+      <c r="E29" s="3">
         <v>15100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>105900</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-14700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>12000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-35300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-54300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-93100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-16400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>68100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-128700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-160500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-97000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-169600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-279700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>426000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,13 +2048,16 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-96100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2030,72 +2099,78 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>257000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-230500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-212500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-84800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-262300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-141300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-264800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-139300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-205800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-362900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>257000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-230500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-212500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-84800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-262300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-141300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-264800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-139300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-205800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-362900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>345300</v>
+      </c>
+      <c r="E41" s="3">
         <v>434000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>426900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>668500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>918300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>636400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>337200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1117700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1602100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1277700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1006200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>788400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>703500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>658400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1099500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1361800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1205200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,64 +2512,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E43" s="3">
         <v>100500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>132700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>126300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>158900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>141900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>155200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>143600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>112700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>150600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>169300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>145100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>154300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>179300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>212700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,64 +2630,70 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>16400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>62400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>75400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>61900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>97400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>107100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>86700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>84600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>107900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>113100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2647,176 +2748,188 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2476100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1880000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1288900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1227000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1460000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1224700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1594400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1445300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1109100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>905300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>873100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>863100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3032800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3237100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3223500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3766400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3866600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>3093400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6614700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6308500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6385200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6815500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6741100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6119700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5470900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5433400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5027300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8252500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9354900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8067900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9218300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10704000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11125800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>701800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1163800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1975900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2006500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1853500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2506900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2589300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1986900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1949000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2002400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1992000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2153900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2367900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2126800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1417000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1969100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2091700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,64 +3043,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E52" s="3">
         <v>108600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>208200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>167000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>176000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>206600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>265400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>257600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3775700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5559100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6782500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4221300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4268900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4549100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>853600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>918200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1076800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3562600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6872100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10757100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10743400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11028500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11740800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11877300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11232200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14197800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15443000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15921300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16625300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20200600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19043100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16183500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19160100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19832200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3268,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>45100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>219400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>185900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>188700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>192000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>114700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>121900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>129400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>83200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>109300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>178400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>113100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>132400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>170700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>177900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,64 +3384,70 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>681500</v>
+      </c>
+      <c r="E59" s="3">
         <v>561300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>711000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>755300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>847100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>998400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>917300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>528300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>570900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>601800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>516800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>494900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>580800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>318100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>374800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>390000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>511200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3363,120 +3502,129 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>371800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3157200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5528100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5455500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5291800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5463100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5679000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5264300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5003200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4714800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4022800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7024000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7938700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7086000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9211100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9453300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9386800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>7500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>224000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>238900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3090700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3837400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4732900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2059600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3865900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4079400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>457100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>469800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>490400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1733600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5181300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9314900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9291100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9367800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10086200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10244000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9841300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12050900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13387100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13812400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14403200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17699100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16457500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13443800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14413600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14616100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3845,16 +4012,16 @@
         <v>794700</v>
       </c>
       <c r="F70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="G70" s="3">
         <v>800300</v>
-      </c>
-      <c r="G70" s="3">
-        <v>800400</v>
       </c>
       <c r="H70" s="3">
         <v>800400</v>
       </c>
       <c r="I70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="J70" s="3">
         <v>854200</v>
@@ -3863,10 +4030,10 @@
         <v>854200</v>
       </c>
       <c r="L70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="M70" s="3">
         <v>916100</v>
-      </c>
-      <c r="M70" s="3">
-        <v>999500</v>
       </c>
       <c r="N70" s="3">
         <v>999500</v>
@@ -3887,10 +4054,13 @@
         <v>999500</v>
       </c>
       <c r="T70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="U70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6842500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1016400</v>
+      </c>
+      <c r="E76" s="3">
         <v>896100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>647500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>652000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>860300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>854300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>779100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>536600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1292700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1139800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1109500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1222500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1502000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1586100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1740300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3746900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4216600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>257000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-230500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-212500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-84800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-262300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-141300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-264800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-139300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-205800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-362900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>485600</v>
+      </c>
+      <c r="E83" s="3">
         <v>128000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>291100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>147400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>145600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>155400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>130900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>138000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>138100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>170100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>190300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>138800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>166400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>273000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>137500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>119400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>233600</v>
+      </c>
+      <c r="E89" s="3">
         <v>99900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>92200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>67800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>120700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>72800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>66800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>76500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>128800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23900</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>47600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-59700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-63700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-979000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-196500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-571600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-258900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>16000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>216300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>60900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-322900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>416500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-950100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>114600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>166900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5136600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,25 +5312,26 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-1600</v>
       </c>
       <c r="G96" s="3">
         <v>-1600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -5125,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-53700</v>
       </c>
       <c r="S96" s="3">
         <v>-53700</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5546,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E100" s="3">
         <v>54500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>182000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>201000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>559300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>213000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>506900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-407900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>99200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1009800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>692700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-329500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-686500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-42900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-455200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-212500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>266300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>324600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-778200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-542200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>337300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>254800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>139700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>71400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-350200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-175100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>108500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>695600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E8" s="3">
         <v>821400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>477100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>675100</v>
       </c>
-      <c r="G8" s="3">
-        <v>250200</v>
-      </c>
       <c r="H8" s="3">
-        <v>301100</v>
+        <v>18500</v>
       </c>
       <c r="I8" s="3">
+        <v>694800</v>
+      </c>
+      <c r="J8" s="3">
         <v>429900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>416600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>257500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>255900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>252200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>237200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>220600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>155400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>123000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>138000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>70200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>552400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>3200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>100200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>206400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>102900</v>
       </c>
-      <c r="H9" s="3">
-        <v>109800</v>
-      </c>
       <c r="I9" s="3">
+        <v>125400</v>
+      </c>
+      <c r="J9" s="3">
         <v>115500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>93600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>87200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>87500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>83000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>86800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>51700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>290700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>818200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>376900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>468700</v>
       </c>
-      <c r="G10" s="3">
-        <v>147300</v>
-      </c>
       <c r="H10" s="3">
-        <v>191300</v>
+        <v>-84400</v>
       </c>
       <c r="I10" s="3">
+        <v>569400</v>
+      </c>
+      <c r="J10" s="3">
         <v>314400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>312100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>163900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>168700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>164700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>103700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>98300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>50600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>261700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,126 +1081,135 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>10800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8500</v>
       </c>
-      <c r="H14" s="3">
-        <v>3300</v>
-      </c>
       <c r="I14" s="3">
+        <v>10100</v>
+      </c>
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>133400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1426800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>471900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E15" s="3">
         <v>36700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>128000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>291100</v>
       </c>
-      <c r="G15" s="3">
-        <v>141600</v>
-      </c>
       <c r="H15" s="3">
-        <v>147400</v>
+        <v>6900</v>
       </c>
       <c r="I15" s="3">
+        <v>44300</v>
+      </c>
+      <c r="J15" s="3">
         <v>145600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>155400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>128600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>132900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>129200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>138200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>139400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>85600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>80600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>74800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>38100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>110100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>551900</v>
+        <v>89800</v>
       </c>
       <c r="E17" s="3">
+        <v>455800</v>
+      </c>
+      <c r="F17" s="3">
         <v>195800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>997400</v>
       </c>
-      <c r="G17" s="3">
-        <v>527200</v>
-      </c>
       <c r="H17" s="3">
-        <v>306900</v>
+        <v>199100</v>
       </c>
       <c r="I17" s="3">
+        <v>741500</v>
+      </c>
+      <c r="J17" s="3">
         <v>468400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>483400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>501200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>280400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>304100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>308600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>390100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>241100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>624600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>161900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1036000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>269500</v>
+        <v>-15400</v>
       </c>
       <c r="E18" s="3">
+        <v>365600</v>
+      </c>
+      <c r="F18" s="3">
         <v>281300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-322300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-277000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-5800</v>
+        <v>-180600</v>
       </c>
       <c r="I18" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-38500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-66800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-243700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-51900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-71400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-169500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-85700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-65900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-486600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-91700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-483600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,13 +1376,14 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>96100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1394,75 +1428,81 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E21" s="3">
         <v>851200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>409200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-135500</v>
-      </c>
       <c r="H21" s="3">
-        <v>141500</v>
+        <v>-39100</v>
       </c>
       <c r="I21" s="3">
+        <v>532600</v>
+      </c>
+      <c r="J21" s="3">
         <v>107100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>88500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-112800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>113500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>86200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>98700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>53100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>100600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-213600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-364300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1520,126 +1560,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E23" s="3">
         <v>365600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>281200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-322400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-277100</v>
-      </c>
       <c r="H23" s="3">
-        <v>-5900</v>
+        <v>-180600</v>
       </c>
       <c r="I23" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-38500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-66800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-243700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-51900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-71400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-169500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-85700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-65900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-486600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-91800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-483700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4300</v>
       </c>
-      <c r="G24" s="3">
-        <v>1000</v>
-      </c>
       <c r="H24" s="3">
-        <v>31200</v>
+        <v>1100</v>
       </c>
       <c r="I24" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-75200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-23200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-13200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-15100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-16600</v>
       </c>
       <c r="E26" s="3">
+        <v>365600</v>
+      </c>
+      <c r="F26" s="3">
         <v>281400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-326700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-278100</v>
-      </c>
       <c r="H26" s="3">
-        <v>-37100</v>
+        <v>-181700</v>
       </c>
       <c r="I26" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-30700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-64300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-236300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-146300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-52600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-471500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-86500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-483900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-30200</v>
       </c>
       <c r="E27" s="3">
+        <v>181400</v>
+      </c>
+      <c r="F27" s="3">
         <v>241900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-336400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-197800</v>
-      </c>
       <c r="H27" s="3">
-        <v>-31400</v>
+        <v>-16600</v>
       </c>
       <c r="I27" s="3">
+        <v>-190100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-49500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-169200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-104300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-432200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-83200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-453100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,67 +1932,73 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-320500</v>
+        <v>-14100</v>
       </c>
       <c r="E29" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="F29" s="3">
         <v>15100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>105900</v>
       </c>
-      <c r="G29" s="3">
-        <v>-14700</v>
-      </c>
       <c r="H29" s="3">
-        <v>12000</v>
+        <v>-111100</v>
       </c>
       <c r="I29" s="3">
+        <v>-192200</v>
+      </c>
+      <c r="J29" s="3">
         <v>-35300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-54300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-93100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-16400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>68100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-128700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-160500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-169600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-279700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>426000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,13 +2118,16 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-96100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2102,75 +2172,81 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-44300</v>
       </c>
       <c r="E33" s="3">
+        <v>125400</v>
+      </c>
+      <c r="F33" s="3">
         <v>257000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-230500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-212500</v>
-      </c>
       <c r="H33" s="3">
-        <v>-19400</v>
+        <v>-127700</v>
       </c>
       <c r="I33" s="3">
+        <v>-382300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-84800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-262300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-141300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-264800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-139300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-205800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-362900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-44300</v>
       </c>
       <c r="E35" s="3">
+        <v>125400</v>
+      </c>
+      <c r="F35" s="3">
         <v>257000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-230500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-212500</v>
-      </c>
       <c r="H35" s="3">
-        <v>-19400</v>
+        <v>-127700</v>
       </c>
       <c r="I35" s="3">
+        <v>-382300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-84800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-262300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-141300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-264800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-139300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-205800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-362900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E41" s="3">
         <v>345300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>434000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>426900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>668500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>918300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>636400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>337200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1117700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1602100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1277700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1006200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>788400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>703500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>658400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1099500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1361800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1205200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,67 +2605,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>85800</v>
+        <v>87700</v>
       </c>
       <c r="E43" s="3">
+        <v>95400</v>
+      </c>
+      <c r="F43" s="3">
         <v>100500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>132700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>126300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>158900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>141900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>155200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>143600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>112700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>94600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>150600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>169300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>145100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>154300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>179300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>212700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2633,8 +2729,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2642,58 +2741,61 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F45" s="3">
         <v>16400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>58000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>62400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>75400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>61900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>97400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>107100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>86700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>84600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>107900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>113100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2751,67 +2853,73 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2488800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2476100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1880000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1288900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1227000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1460000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1224700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1594400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1445300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1109100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>905300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>873100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>863100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3032800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3237100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3223500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3766400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3866600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2819,117 +2927,123 @@
         <v>8</v>
       </c>
       <c r="E48" s="3">
+        <v>41100</v>
+      </c>
+      <c r="F48" s="3">
         <v>3093400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6614700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6308500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6385200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6815500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6741100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6119700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5470900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5433400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5027300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8252500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9354900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8067900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9218300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10704000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11125800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>701800</v>
+        <v>560700</v>
       </c>
       <c r="E49" s="3">
+        <v>569700</v>
+      </c>
+      <c r="F49" s="3">
         <v>1163800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1975900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2006500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1853500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2506900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2589300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1986900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1949000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2002400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1992000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2153900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2367900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2126800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1417000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1969100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2091700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,67 +3163,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E52" s="3">
         <v>6600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>108600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>208200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>167000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>176000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>206600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>265400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>257600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3775700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5559100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6782500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4221300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4268900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4549100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>853600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>918200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1076800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3463800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3562600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6872100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10757100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10743400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11028500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11740800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11877300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11232200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14197800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15443000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15921300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16625300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20200600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19043100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16183500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19160100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19832200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,8 +3399,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3278,58 +3409,61 @@
         <v>8</v>
       </c>
       <c r="E57" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F57" s="3">
         <v>45100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>219400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>188700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>192000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>121900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>129400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>83200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>109300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>178400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>113100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>132400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>170700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>177900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3387,67 +3521,73 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>681500</v>
+        <v>574000</v>
       </c>
       <c r="E59" s="3">
+        <v>632000</v>
+      </c>
+      <c r="F59" s="3">
         <v>561300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>711000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>755300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>847100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>998400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>917300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>528300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>570900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>601800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>516800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>494900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>580800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>318100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>374800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>390000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>511200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3505,126 +3645,135 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>366500</v>
+      </c>
+      <c r="E61" s="3">
         <v>371800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3157200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5528100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5455500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5291800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5463100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5679000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5264300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5003200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4714800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4022800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7024000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7938700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7086000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9211100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9453300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9386800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F62" s="3">
         <v>7500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>224000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>238900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3090700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3837400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4732900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2059600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3865900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4079400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>457100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>469800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>490400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1733600</v>
+        <v>1645400</v>
       </c>
       <c r="E66" s="3">
+        <v>1751500</v>
+      </c>
+      <c r="F66" s="3">
         <v>5181300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9314900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9291100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9367800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10086200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10244000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9841300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12050900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13387100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13812400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14403200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17699100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16457500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13443800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14413600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14616100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4015,16 +4183,16 @@
         <v>794700</v>
       </c>
       <c r="G70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="H70" s="3">
         <v>800300</v>
-      </c>
-      <c r="H70" s="3">
-        <v>800400</v>
       </c>
       <c r="I70" s="3">
         <v>800400</v>
       </c>
       <c r="J70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="K70" s="3">
         <v>854200</v>
@@ -4033,10 +4201,10 @@
         <v>854200</v>
       </c>
       <c r="M70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="N70" s="3">
         <v>916100</v>
-      </c>
-      <c r="N70" s="3">
-        <v>999500</v>
       </c>
       <c r="O70" s="3">
         <v>999500</v>
@@ -4057,10 +4225,13 @@
         <v>999500</v>
       </c>
       <c r="U70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="V70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6888500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1023800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1016400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>896100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>647500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>652000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>860300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>854300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>779100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>536600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1292700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1139800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1109500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1222500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1502000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1586100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1740300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3746900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4216600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-44300</v>
       </c>
       <c r="E81" s="3">
+        <v>125400</v>
+      </c>
+      <c r="F81" s="3">
         <v>257000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-230500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-212500</v>
-      </c>
       <c r="H81" s="3">
-        <v>-19400</v>
+        <v>-127700</v>
       </c>
       <c r="I81" s="3">
+        <v>-382300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-84800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-262300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-141300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-264800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-139300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-205800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-362900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E83" s="3">
         <v>485600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>128000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>291100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>141600</v>
       </c>
-      <c r="H83" s="3">
-        <v>147400</v>
-      </c>
       <c r="I83" s="3">
+        <v>579300</v>
+      </c>
+      <c r="J83" s="3">
         <v>145600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>155400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>130900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>138000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>138100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>170100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>190300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>138800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>166400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>273000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>137500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>119400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E89" s="3">
         <v>233600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>99900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>92200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20200</v>
       </c>
-      <c r="H89" s="3">
-        <v>67800</v>
-      </c>
       <c r="I89" s="3">
+        <v>262600</v>
+      </c>
+      <c r="J89" s="3">
         <v>120700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>66800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>76500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>128800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23900</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>47600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>42300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-59700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-63700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-979000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-196500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-571600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-258900</v>
       </c>
-      <c r="H94" s="3">
-        <v>16000</v>
-      </c>
       <c r="I94" s="3">
+        <v>-1913400</v>
+      </c>
+      <c r="J94" s="3">
         <v>216300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>60900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-322900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>416500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-950100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>114600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>166900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5136600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,28 +5546,29 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-6500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-1600</v>
       </c>
       <c r="H96" s="3">
         <v>-1600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -5361,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-53700</v>
       </c>
       <c r="T96" s="3">
         <v>-53700</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,181 +5792,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E100" s="3">
         <v>58200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>54500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>26800</v>
       </c>
-      <c r="H100" s="3">
-        <v>182000</v>
-      </c>
       <c r="I100" s="3">
+        <v>923800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-18600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>201000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>559300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>213000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>506900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-407900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>99200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1009800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>692700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-329500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
-        <v>600</v>
-      </c>
       <c r="I101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-686500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-455200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-212500</v>
       </c>
-      <c r="H102" s="3">
-        <v>266300</v>
-      </c>
       <c r="I102" s="3">
+        <v>-729500</v>
+      </c>
+      <c r="J102" s="3">
         <v>324600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-778200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-542200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>337300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>254800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>139700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>71400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-350200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-175100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>108500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>695600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>390300</v>
+      </c>
+      <c r="E8" s="3">
         <v>74400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>821400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>477100</v>
       </c>
-      <c r="G8" s="3">
-        <v>675100</v>
-      </c>
       <c r="H8" s="3">
+        <v>189900</v>
+      </c>
+      <c r="I8" s="3">
         <v>18500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>694800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>429900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>416600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>257500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>255900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>252200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>237200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>220600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>155400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>123000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>138000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>70200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>552400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
         <v>3200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>206400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>102900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>125400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>115500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>93600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>87200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>83000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>86800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>51700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>42000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>290700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3">
         <v>818200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>376900</v>
       </c>
-      <c r="G10" s="3">
-        <v>468700</v>
-      </c>
       <c r="H10" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="I10" s="3">
         <v>-84400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>569400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>314400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>312100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>163900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>168700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>164700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>133800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>103700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>98300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>50600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>261700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,132 +1101,141 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
-        <v>9600</v>
-      </c>
       <c r="H14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I14" s="3">
         <v>8500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>133400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>43300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1426800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>471900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E15" s="3">
         <v>9200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>128000</v>
       </c>
-      <c r="G15" s="3">
-        <v>291100</v>
-      </c>
       <c r="H15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I15" s="3">
         <v>6900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>145600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>155400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>128600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>132900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>129200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>138200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>139400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>85600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>80600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>74800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>38100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>110100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>259700</v>
+      </c>
+      <c r="E17" s="3">
         <v>89800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>455800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>195800</v>
       </c>
-      <c r="G17" s="3">
-        <v>997400</v>
-      </c>
       <c r="H17" s="3">
+        <v>144200</v>
+      </c>
+      <c r="I17" s="3">
         <v>199100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>741500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>468400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>483400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>501200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>280400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>304100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>308600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>390100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>241100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>188900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>624600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>161900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1036000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>365600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>281300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-322300</v>
-      </c>
       <c r="H18" s="3">
+        <v>45800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-180600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-46700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-66800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-243700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-51900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-71400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-169500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-85700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-65900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-486600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-91700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-483600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1431,78 +1465,84 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>851200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>409200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-31200</v>
-      </c>
       <c r="H21" s="3">
+        <v>195300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-39100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>532600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>107100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>88500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-112800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>113500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>86200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>53100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>100600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-213600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-364300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1563,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>365600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>281200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-322400</v>
-      </c>
       <c r="H23" s="3">
+        <v>45700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-180600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-46700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-66800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-243700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-51900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-71400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-169500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-85700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-65900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-486600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-91800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-483700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>4300</v>
-      </c>
       <c r="H24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-75200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-18700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-13200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-15100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>365600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>281400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-326700</v>
-      </c>
       <c r="H26" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-181700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-59800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-236300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-146300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-67000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-52600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-471500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-86500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-483900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>181400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>241900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-336400</v>
-      </c>
       <c r="H27" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-190100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-169200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-104300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-42400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-432200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-83200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-453100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,70 +1993,76 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-14100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-56000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>15100</v>
       </c>
-      <c r="G29" s="3">
-        <v>105900</v>
-      </c>
       <c r="H29" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="I29" s="3">
         <v>-111100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-192200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-35300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-54300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-93100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-16400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>68100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-128700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-160500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-97000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-169600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-279700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>426000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2175,78 +2245,84 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>125400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>257000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-230500</v>
-      </c>
       <c r="H33" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-127700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-382300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-84800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-49000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-262300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-141300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-264800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-139300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-205800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-362900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>125400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>257000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-230500</v>
-      </c>
       <c r="H35" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-127700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-382300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-84800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-49000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-262300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-141300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-264800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-139300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-205800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-362900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>261200</v>
+      </c>
+      <c r="E41" s="3">
         <v>247400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>345300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>434000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>426900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>668500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>918300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>636400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>337200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1117700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1602100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1277700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1006200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>788400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>703500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>658400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1099500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1361800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1205200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,70 +2698,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E43" s="3">
         <v>87700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>95400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>132700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>126300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>158900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>141900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>155200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>143600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>112700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>94600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>150600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>169300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>145100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>154300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>179300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>212700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2732,70 +2828,76 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>67300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>62400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>75400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>61900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>97400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>107100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>86700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>84600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>107900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>113100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2856,194 +2958,206 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2517700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2488800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2476100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1880000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1288900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1227000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1460000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1224700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1594400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1445300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1109100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>905300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>873100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>863100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3032800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3237100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3223500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3766400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3866600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3093400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6614700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6308500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6385200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6815500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6741100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6119700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5470900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5433400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5027300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8252500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9354900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8067900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9218300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10704000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11125800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>553300</v>
+      </c>
+      <c r="E49" s="3">
         <v>560700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>569700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1163800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1975900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2006500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1853500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2506900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2589300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1986900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1949000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2002400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1992000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2153900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2367900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2126800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1417000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1969100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2091700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,70 +3283,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>108600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>208200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>167000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>176000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>206600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>265400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>257600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3775700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5559100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6782500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4221300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4268900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4549100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>853600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>918200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1076800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3502400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3463800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3562600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6872100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10757100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10743400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11028500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11740800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11877300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11232200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14197800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15443000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15921300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16625300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20200600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19043100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16183500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19160100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19832200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>219400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>188700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>192000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>114700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>121900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>129400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>83200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>109300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>178400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>113100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>132400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>170700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>177900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3524,70 +3658,76 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>701100</v>
+      </c>
+      <c r="E59" s="3">
         <v>574000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>632000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>561300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>711000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>755300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>847100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>998400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>917300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>528300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>570900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>601800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>516800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>494900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>580800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>318100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>374800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>390000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>511200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3648,132 +3788,141 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E61" s="3">
         <v>366500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>371800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3157200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5528100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5455500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5291800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5463100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5679000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5264300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5003200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4714800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4022800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7024000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7938700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7086000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9211100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9453300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9386800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>224000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>238900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3090700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3837400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4732900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2059600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3865900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4079400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>457100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>469800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>490400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1645400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1751500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5181300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9314900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9291100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9367800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10086200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10244000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9841300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12050900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13387100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13812400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14403200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17699100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16457500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13443800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14413600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14616100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4186,16 +4354,16 @@
         <v>794700</v>
       </c>
       <c r="H70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="I70" s="3">
         <v>800300</v>
-      </c>
-      <c r="I70" s="3">
-        <v>800400</v>
       </c>
       <c r="J70" s="3">
         <v>800400</v>
       </c>
       <c r="K70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="L70" s="3">
         <v>854200</v>
@@ -4204,10 +4372,10 @@
         <v>854200</v>
       </c>
       <c r="N70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="O70" s="3">
         <v>916100</v>
-      </c>
-      <c r="O70" s="3">
-        <v>999500</v>
       </c>
       <c r="P70" s="3">
         <v>999500</v>
@@ -4228,10 +4396,13 @@
         <v>999500</v>
       </c>
       <c r="V70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="W70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6813400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1177800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1023800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1016400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>896100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>647500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>652000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>860300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>854300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>779100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>536600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1292700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1139800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1109500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1222500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1502000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1586100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1740300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3746900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4216600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>125400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>257000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-230500</v>
-      </c>
       <c r="H81" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-127700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-382300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-84800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-49000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-262300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-141300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-264800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-139300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-205800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-362900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E83" s="3">
         <v>9200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>485600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>128000</v>
       </c>
-      <c r="G83" s="3">
-        <v>291100</v>
-      </c>
       <c r="H83" s="3">
+        <v>149600</v>
+      </c>
+      <c r="I83" s="3">
         <v>141600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>579300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>145600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>155400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>138000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>170100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>190300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>138800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>166400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>273000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>137500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>119400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>233600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>99900</v>
       </c>
-      <c r="G89" s="3">
-        <v>92200</v>
-      </c>
       <c r="H89" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I89" s="3">
         <v>20200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>262600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>120700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>72800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>66800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>76500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>128800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>47600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>42300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-59700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-63700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,16 +5495,17 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-3100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-979000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-196500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-571600</v>
-      </c>
       <c r="H94" s="3">
+        <v>-312700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-258900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>216300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>60900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-322900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>416500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-950100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>114600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>166900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5136600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,22 +5780,23 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-6500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-3200</v>
       </c>
       <c r="H96" s="3">
         <v>-1600</v>
@@ -5571,7 +5805,7 @@
         <v>-1600</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5598,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-53700</v>
       </c>
       <c r="U96" s="3">
         <v>-53700</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>58200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>54500</v>
       </c>
-      <c r="G100" s="3">
-        <v>24100</v>
-      </c>
       <c r="H100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I100" s="3">
         <v>26800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>923800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>201000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>559300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>213000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>506900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-407900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>99200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1009800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>692700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-329500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
-        <v>100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="N101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="P101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>3900</v>
+      </c>
+      <c r="S101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="T101" s="3">
         <v>-2500</v>
       </c>
-      <c r="J101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="O101" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>3900</v>
-      </c>
-      <c r="R101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-98100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-686500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42900</v>
       </c>
-      <c r="G102" s="3">
-        <v>-455200</v>
-      </c>
       <c r="H102" s="3">
+        <v>-242600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-212500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-729500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>324600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-778200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-542200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>337300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>254800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>139700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>71400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>63600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-350200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-175100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>108500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>695600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>390300</v>
+        <v>74000</v>
       </c>
       <c r="E8" s="3">
-        <v>74400</v>
+        <v>387000</v>
       </c>
       <c r="F8" s="3">
-        <v>821400</v>
+        <v>71900</v>
       </c>
       <c r="G8" s="3">
-        <v>477100</v>
+        <v>350300</v>
       </c>
       <c r="H8" s="3">
-        <v>189900</v>
+        <v>261500</v>
       </c>
       <c r="I8" s="3">
-        <v>18500</v>
+        <v>188500</v>
       </c>
       <c r="J8" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K8" s="3">
         <v>694800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>429900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>416600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>257500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>255900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>252200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>237200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>220600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>155400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>123000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>138000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>70200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>552400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -830,127 +837,133 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>206400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>102900</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>125400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>115500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>93600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>87200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>83000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>86800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>51700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>42000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>290700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>387000</v>
       </c>
       <c r="F10" s="3">
-        <v>818200</v>
+        <v>71900</v>
       </c>
       <c r="G10" s="3">
-        <v>376900</v>
+        <v>350300</v>
       </c>
       <c r="H10" s="3">
-        <v>-16500</v>
+        <v>261500</v>
       </c>
       <c r="I10" s="3">
-        <v>-84400</v>
+        <v>188500</v>
       </c>
       <c r="J10" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K10" s="3">
         <v>569400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>314400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>312100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>168700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>164700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>103700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>81000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>98300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>50600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>261700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,138 +1121,147 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-277800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>10100</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N14" s="3">
+        <v>133400</v>
+      </c>
+      <c r="O14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>8500</v>
-      </c>
-      <c r="J14" s="3">
-        <v>10100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>3900</v>
-      </c>
-      <c r="L14" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M14" s="3">
-        <v>133400</v>
-      </c>
-      <c r="N14" s="3">
-        <v>3200</v>
-      </c>
-      <c r="O14" s="3">
-        <v>900</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>43300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1426800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>471900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>8100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9200</v>
       </c>
-      <c r="F15" s="3">
-        <v>36700</v>
-      </c>
       <c r="G15" s="3">
-        <v>128000</v>
+        <v>9100</v>
       </c>
       <c r="H15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I15" s="3">
         <v>11400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>145600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>155400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>128600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>132900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>129200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>138200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>139400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>85600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>80600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>74800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>38100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>110100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>259700</v>
+        <v>68300</v>
       </c>
       <c r="E17" s="3">
-        <v>89800</v>
+        <v>261400</v>
       </c>
       <c r="F17" s="3">
-        <v>455800</v>
+        <v>75400</v>
       </c>
       <c r="G17" s="3">
-        <v>195800</v>
+        <v>198700</v>
       </c>
       <c r="H17" s="3">
-        <v>144200</v>
+        <v>151800</v>
       </c>
       <c r="I17" s="3">
-        <v>199100</v>
+        <v>124100</v>
       </c>
       <c r="J17" s="3">
+        <v>36700</v>
+      </c>
+      <c r="K17" s="3">
         <v>741500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>468400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>483400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>501200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>280400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>304100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>308600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>390100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>241100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>188900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>624600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>161900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1036000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>130600</v>
+        <v>5800</v>
       </c>
       <c r="E18" s="3">
-        <v>-15400</v>
+        <v>125600</v>
       </c>
       <c r="F18" s="3">
-        <v>365600</v>
+        <v>-3600</v>
       </c>
       <c r="G18" s="3">
-        <v>281300</v>
+        <v>151600</v>
       </c>
       <c r="H18" s="3">
-        <v>45800</v>
+        <v>109700</v>
       </c>
       <c r="I18" s="3">
-        <v>-180600</v>
+        <v>64400</v>
       </c>
       <c r="J18" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-46700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-66800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-243700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-51900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-169500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-85700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-65900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-486600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-91700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-483600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,31 +1444,32 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-5900</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-8800</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1468,104 +1502,110 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>138700</v>
+        <v>19900</v>
       </c>
       <c r="E21" s="3">
-        <v>-6200</v>
+        <v>142500</v>
       </c>
       <c r="F21" s="3">
-        <v>851200</v>
+        <v>-300</v>
       </c>
       <c r="G21" s="3">
-        <v>409200</v>
+        <v>155200</v>
       </c>
       <c r="H21" s="3">
-        <v>195300</v>
+        <v>96700</v>
       </c>
       <c r="I21" s="3">
-        <v>-39100</v>
+        <v>72400</v>
       </c>
       <c r="J21" s="3">
+        <v>-165600</v>
+      </c>
+      <c r="K21" s="3">
         <v>532600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>107100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-112800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>113500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>86200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>98700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>53100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-213600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-364300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E23" s="3">
         <v>130600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15400</v>
       </c>
-      <c r="F23" s="3">
-        <v>365600</v>
-      </c>
       <c r="G23" s="3">
-        <v>281200</v>
+        <v>140900</v>
       </c>
       <c r="H23" s="3">
+        <v>359700</v>
+      </c>
+      <c r="I23" s="3">
         <v>45700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-180600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-66800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-243700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-51900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-169500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-85700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-65900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-486600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-91800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-483700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
-        <v>-100</v>
+        <v>-3900</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-75200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-23200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-18700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-13200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-15100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E26" s="3">
         <v>130700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16600</v>
       </c>
-      <c r="F26" s="3">
-        <v>365600</v>
-      </c>
       <c r="G26" s="3">
-        <v>281400</v>
+        <v>144800</v>
       </c>
       <c r="H26" s="3">
+        <v>359600</v>
+      </c>
+      <c r="I26" s="3">
         <v>43000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-181700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-59800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-236300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-40900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-146300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-67000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-52600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-471500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-86500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-483900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>108800</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>-30200</v>
+        <v>75100</v>
       </c>
       <c r="F27" s="3">
-        <v>181400</v>
+        <v>-43300</v>
       </c>
       <c r="G27" s="3">
-        <v>241900</v>
+        <v>100600</v>
       </c>
       <c r="H27" s="3">
-        <v>33700</v>
+        <v>257000</v>
       </c>
       <c r="I27" s="3">
-        <v>-16600</v>
+        <v>-18000</v>
       </c>
       <c r="J27" s="3">
+        <v>-212500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-190100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-49500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-169200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-104300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-42400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-432200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-83200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-453100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,73 +2054,79 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-33600</v>
+        <v>1400</v>
       </c>
       <c r="E29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F29" s="3">
         <v>-14100</v>
       </c>
-      <c r="F29" s="3">
-        <v>-56000</v>
-      </c>
       <c r="G29" s="3">
-        <v>15100</v>
+        <v>-33500</v>
       </c>
       <c r="H29" s="3">
-        <v>-56200</v>
+        <v>-80900</v>
       </c>
       <c r="I29" s="3">
-        <v>-111100</v>
+        <v>-95500</v>
       </c>
       <c r="J29" s="3">
+        <v>-110600</v>
+      </c>
+      <c r="K29" s="3">
         <v>-192200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-35300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-54300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-93100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-16400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>68100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-128700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-160500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-97000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-169600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-279700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>426000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,31 +2258,34 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-5900</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-5500</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-22300</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-153000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2248,81 +2318,87 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>75100</v>
+        <v>13800</v>
       </c>
       <c r="E33" s="3">
-        <v>-44300</v>
+        <v>91400</v>
       </c>
       <c r="F33" s="3">
-        <v>125400</v>
+        <v>-29600</v>
       </c>
       <c r="G33" s="3">
-        <v>257000</v>
+        <v>115300</v>
       </c>
       <c r="H33" s="3">
-        <v>-22400</v>
+        <v>276500</v>
       </c>
       <c r="I33" s="3">
-        <v>-127700</v>
+        <v>-8700</v>
       </c>
       <c r="J33" s="3">
+        <v>-197800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-382300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-84800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-49000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-262300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-141300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-264800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-139300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-205800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-362900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>75100</v>
+        <v>13800</v>
       </c>
       <c r="E35" s="3">
-        <v>-44300</v>
+        <v>91400</v>
       </c>
       <c r="F35" s="3">
-        <v>125400</v>
+        <v>-29600</v>
       </c>
       <c r="G35" s="3">
-        <v>257000</v>
+        <v>115300</v>
       </c>
       <c r="H35" s="3">
-        <v>-22400</v>
+        <v>276500</v>
       </c>
       <c r="I35" s="3">
-        <v>-127700</v>
+        <v>-8700</v>
       </c>
       <c r="J35" s="3">
+        <v>-197800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-382300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-84800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-49000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-262300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-141300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-264800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-139300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-205800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-362900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>294400</v>
+      </c>
+      <c r="E41" s="3">
         <v>261200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>345300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>434000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>426900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>668500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>918300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>636400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>337200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1117700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1602100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1277700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1006200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>788400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>703500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>658400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1099500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1361800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1205200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,96 +2791,102 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E43" s="3">
         <v>103000</v>
       </c>
-      <c r="E43" s="3">
-        <v>87700</v>
-      </c>
       <c r="F43" s="3">
+        <v>94800</v>
+      </c>
+      <c r="G43" s="3">
         <v>95400</v>
       </c>
-      <c r="G43" s="3">
-        <v>100500</v>
-      </c>
       <c r="H43" s="3">
-        <v>132700</v>
+        <v>153000</v>
       </c>
       <c r="I43" s="3">
-        <v>127000</v>
+        <v>182100</v>
       </c>
       <c r="J43" s="3">
+        <v>173300</v>
+      </c>
+      <c r="K43" s="3">
         <v>126300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>158900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>141900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>155200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>143600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>112700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>150600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>169300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>145100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>154300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>179300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>212700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2831,96 +2927,102 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+        <v>13200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13600</v>
       </c>
       <c r="F45" s="3">
-        <v>3000</v>
+        <v>14500</v>
       </c>
       <c r="G45" s="3">
-        <v>16400</v>
+        <v>18700</v>
       </c>
       <c r="H45" s="3">
-        <v>21900</v>
+        <v>31900</v>
       </c>
       <c r="I45" s="3">
-        <v>27300</v>
+        <v>91700</v>
       </c>
       <c r="J45" s="3">
+        <v>67200</v>
+      </c>
+      <c r="K45" s="3">
         <v>28800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>67300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>75400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>61900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>97400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>107100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>86700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>107900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>113100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>412800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>382500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>361400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>464400</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>723500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>855400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1064700</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2961,203 +3063,215 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2517700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2488800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2476100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1880000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1288900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1227000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1460000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1224700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1594400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1445300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1109100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>905300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>873100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>863100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3032800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3237100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3223500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3766400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3866600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E48" s="3">
         <v>40100</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F48" s="3">
+        <v>42000</v>
+      </c>
+      <c r="G48" s="3">
         <v>41100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3093400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6614700</v>
       </c>
-      <c r="I48" s="3">
-        <v>6308500</v>
-      </c>
       <c r="J48" s="3">
+        <v>6425900</v>
+      </c>
+      <c r="K48" s="3">
         <v>6385200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6815500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6741100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6119700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5470900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5433400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5027300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8252500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9354900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8067900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9218300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10704000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11125800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>547300</v>
+      </c>
+      <c r="E49" s="3">
         <v>553300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>560700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>569700</v>
       </c>
-      <c r="G49" s="3">
-        <v>1163800</v>
-      </c>
       <c r="H49" s="3">
-        <v>1975900</v>
+        <v>576900</v>
       </c>
       <c r="I49" s="3">
-        <v>2006500</v>
+        <v>1197800</v>
       </c>
       <c r="J49" s="3">
+        <v>1196700</v>
+      </c>
+      <c r="K49" s="3">
         <v>1853500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2506900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2589300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1986900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1949000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2002400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1992000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2153900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2367900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2126800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1417000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1969100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2091700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5300</v>
+        <v>2500</v>
       </c>
       <c r="E52" s="3">
-        <v>5400</v>
+        <v>8800</v>
       </c>
       <c r="F52" s="3">
-        <v>6600</v>
+        <v>10900</v>
       </c>
       <c r="G52" s="3">
-        <v>108600</v>
+        <v>11200</v>
       </c>
       <c r="H52" s="3">
-        <v>208200</v>
+        <v>11400</v>
       </c>
       <c r="I52" s="3">
-        <v>167000</v>
+        <v>22200</v>
       </c>
       <c r="J52" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K52" s="3">
         <v>176000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>206600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>265400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>257600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3775700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5559100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6782500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4221300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4268900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4549100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>853600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>918200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1076800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3542900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3502400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3463800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3562600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6872100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10757100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10743400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11028500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11740800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11877300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11232200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14197800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15443000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15921300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16625300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20200600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19043100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16183500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19160100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19832200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E57" s="3">
         <v>17400</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F57" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G57" s="3">
         <v>13800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>219400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>185900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>188700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>192000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>114700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>121900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>129400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>83200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>109300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>178400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>113100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>132400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>170700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>177900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3611,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3661,96 +3795,102 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>701100</v>
+        <v>74800</v>
       </c>
       <c r="E59" s="3">
-        <v>574000</v>
+        <v>84700</v>
       </c>
       <c r="F59" s="3">
-        <v>632000</v>
+        <v>81700</v>
       </c>
       <c r="G59" s="3">
-        <v>561300</v>
+        <v>74200</v>
       </c>
       <c r="H59" s="3">
-        <v>711000</v>
+        <v>80600</v>
       </c>
       <c r="I59" s="3">
-        <v>755300</v>
+        <v>88000</v>
       </c>
       <c r="J59" s="3">
+        <v>71800</v>
+      </c>
+      <c r="K59" s="3">
         <v>847100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>998400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>917300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>528300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>570900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>601800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>516800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>494900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>580800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>318100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>374800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>390000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>511200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>657000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>663300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>481600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>519800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>428100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>521700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>494000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3791,138 +3931,147 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>295300</v>
+        <v>340700</v>
       </c>
       <c r="E61" s="3">
-        <v>366500</v>
+        <v>339800</v>
       </c>
       <c r="F61" s="3">
-        <v>371800</v>
+        <v>412600</v>
       </c>
       <c r="G61" s="3">
-        <v>3157200</v>
+        <v>411400</v>
       </c>
       <c r="H61" s="3">
-        <v>5528100</v>
+        <v>3207100</v>
       </c>
       <c r="I61" s="3">
-        <v>5455500</v>
+        <v>5835400</v>
       </c>
       <c r="J61" s="3">
+        <v>5782200</v>
+      </c>
+      <c r="K61" s="3">
         <v>5291800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5463100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5679000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5264300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5003200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4714800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4022800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7024000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7938700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7086000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9211100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9453300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9386800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9600</v>
+        <v>28900</v>
       </c>
       <c r="E62" s="3">
-        <v>900</v>
+        <v>27300</v>
       </c>
       <c r="F62" s="3">
-        <v>8600</v>
+        <v>35900</v>
       </c>
       <c r="G62" s="3">
-        <v>7500</v>
+        <v>111900</v>
       </c>
       <c r="H62" s="3">
-        <v>24300</v>
+        <v>166500</v>
       </c>
       <c r="I62" s="3">
-        <v>16800</v>
+        <v>140400</v>
       </c>
       <c r="J62" s="3">
+        <v>134600</v>
+      </c>
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>224000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>238900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3090700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3837400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4732900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2059600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3865900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4079400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>457100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>469800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>490400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1530000</v>
+        <v>1036600</v>
       </c>
       <c r="E66" s="3">
-        <v>1645400</v>
+        <v>1039700</v>
       </c>
       <c r="F66" s="3">
-        <v>1751500</v>
+        <v>941400</v>
       </c>
       <c r="G66" s="3">
-        <v>5181300</v>
+        <v>1053400</v>
       </c>
       <c r="H66" s="3">
-        <v>9314900</v>
+        <v>3846800</v>
       </c>
       <c r="I66" s="3">
-        <v>9291100</v>
+        <v>6596100</v>
       </c>
       <c r="J66" s="3">
+        <v>6484200</v>
+      </c>
+      <c r="K66" s="3">
         <v>9367800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10086200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10244000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9841300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12050900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13387100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13812400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14403200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17699100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16457500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13443800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14413600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14616100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4357,16 +4525,16 @@
         <v>794700</v>
       </c>
       <c r="I70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="J70" s="3">
         <v>800300</v>
-      </c>
-      <c r="J70" s="3">
-        <v>800400</v>
       </c>
       <c r="K70" s="3">
         <v>800400</v>
       </c>
       <c r="L70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="M70" s="3">
         <v>854200</v>
@@ -4375,10 +4543,10 @@
         <v>854200</v>
       </c>
       <c r="O70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="P70" s="3">
         <v>916100</v>
-      </c>
-      <c r="P70" s="3">
-        <v>999500</v>
       </c>
       <c r="Q70" s="3">
         <v>999500</v>
@@ -4399,10 +4567,13 @@
         <v>999500</v>
       </c>
       <c r="W70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="X70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6816100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1185600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1177800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1023800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1016400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>896100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>647500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>652000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>860300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>854300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>779100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>536600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1292700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1139800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1109500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1222500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1502000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1586100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1740300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3746900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4216600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>75100</v>
+        <v>13800</v>
       </c>
       <c r="E81" s="3">
-        <v>-44300</v>
+        <v>91400</v>
       </c>
       <c r="F81" s="3">
-        <v>125400</v>
+        <v>-29600</v>
       </c>
       <c r="G81" s="3">
-        <v>257000</v>
+        <v>115300</v>
       </c>
       <c r="H81" s="3">
-        <v>-22400</v>
+        <v>276500</v>
       </c>
       <c r="I81" s="3">
-        <v>-127700</v>
+        <v>-8700</v>
       </c>
       <c r="J81" s="3">
+        <v>-197800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-382300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-84800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-49000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-262300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-141300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-264800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-139300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-205800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-362900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8100</v>
+        <v>119200</v>
       </c>
       <c r="E83" s="3">
-        <v>9200</v>
+        <v>138700</v>
       </c>
       <c r="F83" s="3">
-        <v>485600</v>
+        <v>135400</v>
       </c>
       <c r="G83" s="3">
-        <v>128000</v>
+        <v>-266000</v>
       </c>
       <c r="H83" s="3">
-        <v>149600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>141600</v>
+        <v>110800</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
+        <v>85700</v>
+      </c>
+      <c r="K83" s="3">
         <v>579300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>145600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>155400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>130900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>138000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>138100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>170100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>190300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>138800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>166400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>273000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>137500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>119400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E89" s="3">
         <v>22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27000</v>
       </c>
-      <c r="F89" s="3">
-        <v>233600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>99900</v>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H89" s="3">
-        <v>72000</v>
+        <v>100200</v>
       </c>
       <c r="I89" s="3">
-        <v>20200</v>
+        <v>72100</v>
       </c>
       <c r="J89" s="3">
+        <v>19700</v>
+      </c>
+      <c r="K89" s="3">
         <v>262600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>120700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>72800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>66800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>76500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>128800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23900</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>47600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>42300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-59700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-63700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,31 +5716,32 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E94" s="3">
         <v>4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-979000</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>-196500</v>
       </c>
-      <c r="H94" s="3">
-        <v>-312700</v>
-      </c>
       <c r="I94" s="3">
-        <v>-258900</v>
+        <v>-312400</v>
       </c>
       <c r="J94" s="3">
+        <v>-259100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>216300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>60900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-322900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>416500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-950100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>114600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>166900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5136600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,35 +6014,36 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1700</v>
+        <v>1700</v>
       </c>
       <c r="E96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1600</v>
       </c>
-      <c r="F96" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -5835,10 +6069,10 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-53700</v>
       </c>
       <c r="V96" s="3">
         <v>-53700</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48500</v>
       </c>
-      <c r="F100" s="3">
-        <v>58200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>54500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>923800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>201000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>559300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>213000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>506900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-407900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>99200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1009800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>692700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-329500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
-        <v>800</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S101" s="3">
+        <v>3900</v>
+      </c>
+      <c r="T101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="P101" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>4100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>3900</v>
-      </c>
-      <c r="S101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E102" s="3">
         <v>13800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-98100</v>
       </c>
-      <c r="F102" s="3">
-        <v>-686500</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-42900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-242600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-212500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-729500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>324600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-778200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-542200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>337300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>254800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>139700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>71400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-350200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-175100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>108500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>695600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,178 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E8" s="3">
         <v>74000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>387000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71900</v>
       </c>
-      <c r="G8" s="3">
-        <v>350300</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>261500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>188500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>694800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>429900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>416600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>257500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>255900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>252200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>237200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>220600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>123000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>138000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>70200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>552400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -852,118 +858,124 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>125400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>115500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>93600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>87200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>87500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>86800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>51700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>42000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>290700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E10" s="3">
         <v>74000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>387000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71900</v>
       </c>
-      <c r="G10" s="3">
-        <v>350300</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>261500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>188500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>569400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>314400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>312100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>163900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>168700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>164700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>133800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>103700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>81000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>98300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>50600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>261700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,76 +1140,82 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-40200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-277800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9600</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>133400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>16900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>43300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1426800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>471900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1201,67 +1223,70 @@
         <v>8200</v>
       </c>
       <c r="E15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F15" s="3">
         <v>8100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9200</v>
       </c>
-      <c r="G15" s="3">
-        <v>9100</v>
-      </c>
       <c r="H15" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I15" s="3">
         <v>9300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>145600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>155400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>128600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>132900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>129200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>138200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>139400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>85600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>80600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>74800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>38100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>110100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E17" s="3">
         <v>68300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>261400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>75400</v>
       </c>
-      <c r="G17" s="3">
-        <v>198700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>151800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>124100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>741500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>468400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>483400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>501200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>280400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>304100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>308600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>390100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>241100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>188900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>624600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>161900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1036000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>125600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
-        <v>151600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>109700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>64400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-38500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-66800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-243700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-71400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-169500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-85700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-65900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-486600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-91700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-483600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,35 +1477,36 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5900</v>
       </c>
-      <c r="G20" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>22300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>153000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1505,111 +1538,117 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E21" s="3">
         <v>19900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>142500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
-        <v>155200</v>
-      </c>
       <c r="H21" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I21" s="3">
         <v>96700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>72400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-165600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>532600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>107100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>88500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-112800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>86200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>98700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>53100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-213600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-364300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5200</v>
       </c>
       <c r="G22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>5500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1649,144 +1688,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E23" s="3">
         <v>47800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="G23" s="3">
-        <v>140900</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>359700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-180600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-66800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-243700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-51900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-71400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-169500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-85700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-65900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-486600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-91800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-483700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-75200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-23200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-18700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-13200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-15100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>46900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>130700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16600</v>
       </c>
-      <c r="G26" s="3">
-        <v>144800</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>359600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-181700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-59800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-64300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-236300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-146300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-67000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-52600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-471500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-86500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-483900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>75100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-43300</v>
       </c>
-      <c r="G27" s="3">
-        <v>100600</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>257000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-212500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-190100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-49500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-169200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-104300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-42400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-432200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-83200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-453100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,76 +2114,82 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E29" s="3">
         <v>1400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-14100</v>
       </c>
-      <c r="G29" s="3">
-        <v>-33500</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-80900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-95500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-110600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-192200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-35300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-54300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-93100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-16400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>68100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-128700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-160500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-97000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-169600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-279700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>426000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,35 +2327,38 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E32" s="3">
         <v>5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-22300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-153000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2321,84 +2390,90 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E33" s="3">
         <v>13800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>91400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29600</v>
       </c>
-      <c r="G33" s="3">
-        <v>115300</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>276500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-197800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-382300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-49000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-262300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>41000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-141300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-264800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-139300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-205800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-362900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-27100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E35" s="3">
         <v>13800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>91400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29600</v>
       </c>
-      <c r="G35" s="3">
-        <v>115300</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>276500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-197800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-382300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-49000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-262300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>41000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-141300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-264800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-139300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-205800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-362900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-27100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E41" s="3">
         <v>294400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>261200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>345300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>434000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>426900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>668500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>918300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>636400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>337200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1117700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1602100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1277700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1006200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>788400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>703500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>658400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1099500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1361800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1205200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,76 +2883,82 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E43" s="3">
         <v>101100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>103000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>94800</v>
       </c>
-      <c r="G43" s="3">
-        <v>95400</v>
-      </c>
       <c r="H43" s="3">
+        <v>94700</v>
+      </c>
+      <c r="I43" s="3">
         <v>153000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>182100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>173300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>126300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>158900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>141900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>155200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>143600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>112700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>150600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>169300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>145100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>154300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>179300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>212700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2888,8 +2983,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2930,103 +3025,109 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E45" s="3">
         <v>13200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>91700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>67300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>75400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>61900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>97400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>107100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>86700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>84600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>107900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>113100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E46" s="3">
         <v>412800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>382500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>361400</v>
       </c>
-      <c r="G46" s="3">
-        <v>464400</v>
-      </c>
       <c r="H46" s="3">
+        <v>463700</v>
+      </c>
+      <c r="I46" s="3">
         <v>723500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>855400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1064700</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3066,212 +3167,224 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2492300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2540000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2517700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2488800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2476100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1880000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1288900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1227000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1460000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1224700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1594400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1445300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1109100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>905300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>873100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>863100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3032800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3237100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3223500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3766400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3866600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E48" s="3">
         <v>40200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3093400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6614700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6425900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6385200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6815500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6741100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6119700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5470900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5433400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5027300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8252500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9354900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8067900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9218300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10704000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11125800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>538100</v>
+      </c>
+      <c r="E49" s="3">
         <v>547300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>553300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>560700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>569700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>576900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1197800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1196700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1853500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2506900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2589300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1986900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1949000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2002400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1992000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2153900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2367900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2126800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1417000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1969100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2091700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3522,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10900</v>
       </c>
-      <c r="G52" s="3">
-        <v>11200</v>
-      </c>
       <c r="H52" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I52" s="3">
         <v>11400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>176000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>206600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>265400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>257600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3775700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5559100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6782500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4221300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4268900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4549100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>853600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>918200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1076800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3513300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3542900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3502400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3463800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3562600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6872100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10757100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10743400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11028500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11740800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11877300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11232200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14197800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15443000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15921300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16625300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20200600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19043100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16183500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19160100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19832200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,81 +3791,85 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E57" s="3">
         <v>20500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>219400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>185900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>188700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>192000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>114700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>121900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>129400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>83200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>109300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>178400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>113100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>132400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>170700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>177900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3745,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>9400</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3798,103 +3931,109 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E59" s="3">
         <v>74800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>84700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>81700</v>
       </c>
-      <c r="G59" s="3">
-        <v>74200</v>
-      </c>
       <c r="H59" s="3">
-        <v>80600</v>
+        <v>73600</v>
       </c>
       <c r="I59" s="3">
+        <v>78700</v>
+      </c>
+      <c r="J59" s="3">
         <v>88000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>71800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>847100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>998400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>917300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>528300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>570900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>601800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>516800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>494900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>580800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>318100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>374800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>390000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>511200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>660500</v>
+      </c>
+      <c r="E60" s="3">
         <v>657000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>663300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>481600</v>
       </c>
-      <c r="G60" s="3">
-        <v>519800</v>
-      </c>
       <c r="H60" s="3">
+        <v>510400</v>
+      </c>
+      <c r="I60" s="3">
         <v>428100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>521700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>494000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3934,144 +4073,153 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>329900</v>
+      </c>
+      <c r="E61" s="3">
         <v>340700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>339800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>412600</v>
       </c>
-      <c r="G61" s="3">
-        <v>411400</v>
-      </c>
       <c r="H61" s="3">
+        <v>420800</v>
+      </c>
+      <c r="I61" s="3">
         <v>3207100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5835400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5782200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5291800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5463100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5679000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5264300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5003200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4714800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4022800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7024000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7938700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7086000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9211100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9453300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9386800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E62" s="3">
         <v>28900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>111900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>166500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>140400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>134600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>224000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>238900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3090700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3837400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4732900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2059600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3865900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4079400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>457100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>469800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>490400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1022100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1036600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1039700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>941400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1053400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3846800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6596100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6484200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9367800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10086200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10244000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9841300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12050900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13387100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13812400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14403200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17699100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16457500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13443800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14413600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14616100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4528,16 +4695,16 @@
         <v>794700</v>
       </c>
       <c r="J70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="K70" s="3">
         <v>800300</v>
-      </c>
-      <c r="K70" s="3">
-        <v>800400</v>
       </c>
       <c r="L70" s="3">
         <v>800400</v>
       </c>
       <c r="M70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="N70" s="3">
         <v>854200</v>
@@ -4546,10 +4713,10 @@
         <v>854200</v>
       </c>
       <c r="P70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="Q70" s="3">
         <v>916100</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>999500</v>
       </c>
       <c r="R70" s="3">
         <v>999500</v>
@@ -4570,10 +4737,13 @@
         <v>999500</v>
       </c>
       <c r="X70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6837500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1163900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1185600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1177800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1023800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1016400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>896100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>647500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>652000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>860300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>854300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>779100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>536600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1292700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1139800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1109500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1222500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1502000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1586100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1740300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3746900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4216600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E81" s="3">
         <v>13800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>91400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29600</v>
       </c>
-      <c r="G81" s="3">
-        <v>115300</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>276500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-197800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-382300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-49000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-262300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>41000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-141300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-264800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-139300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-205800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-362900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-27100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>119200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>138700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>135400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-266000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>110800</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>85700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>579300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>145600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>155400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>138000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>138100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>170100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>190300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>138800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>166400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>273000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>137500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>119400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E89" s="3">
         <v>35900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27000</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>72100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>262600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>120700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>72800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>76500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>128800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23900</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>47600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>42300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-59700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-63700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,22 +5936,23 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>8</v>
@@ -5743,8 +5963,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E94" s="3">
         <v>10400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-196500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-312400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-259100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>216300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>60900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-322900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>416500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-950100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>114600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>166900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5136600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6027,13 +6260,13 @@
         <v>1700</v>
       </c>
       <c r="F96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G96" s="3">
         <v>1600</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1600</v>
       </c>
       <c r="I96" s="3">
         <v>1600</v>
@@ -6042,11 +6275,11 @@
         <v>1600</v>
       </c>
       <c r="K96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -6072,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-53700</v>
       </c>
       <c r="W96" s="3">
         <v>-53700</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6529,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48500</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>54500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>923800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>201000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>559300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>213000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>506900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-407900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>99200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1009800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>692700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-329500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>32600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-98100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-42900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-242600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-212500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-729500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>324600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-778200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-542200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>337300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>254800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>139700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>71400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>63600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-350200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-175100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>108500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>695600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,184 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E8" s="3">
         <v>62200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>74000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>387000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71900</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>261500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>188500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>694800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>429900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>416600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>257500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>255900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>252200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>237200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>220600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>123000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>138000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>70200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>552400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -861,121 +868,127 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>125400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>115500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>93600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>87200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>87500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>83000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>51700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>42000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>290700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E10" s="3">
         <v>62200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>387000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71900</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>261500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>188500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>569400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>314400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>312100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>168700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>164700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>133800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>103700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>98300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>50600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>261700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,150 +1160,159 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="3">
         <v>39600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-40200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-277800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9600</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>133400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>16900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>43300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1426800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>471900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8200</v>
+        <v>7200</v>
       </c>
       <c r="E15" s="3">
         <v>8200</v>
       </c>
       <c r="F15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G15" s="3">
         <v>8100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>44300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>145600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>155400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>128600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>132900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>129200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>138200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>139400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>85600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>80600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>74800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>38100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>110100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E17" s="3">
         <v>58200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>68300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>261400</v>
       </c>
-      <c r="G17" s="3">
-        <v>75400</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="3">
+        <v>75500</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>151800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>741500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>468400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>483400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>501200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>280400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>304100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>308600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>390100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>241100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>188900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>624600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>161900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1036000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>125600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>109700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>64400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-66800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-243700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-51900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-71400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-169500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-85700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-65900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-486600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-91700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-483600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,38 +1511,39 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-45300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5900</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>153000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1541,117 +1575,123 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>57600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>142500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>96700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>72400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-165600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>532600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>107100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>88500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-112800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>86200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>98700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>53100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-213600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>45700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-364300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1691,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>130600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15400</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>359700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-180600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-66800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-243700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-51900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-71400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-169500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-85700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-65900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-486600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-91800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-483700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-75200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-23200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-18700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-13200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-15100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E26" s="3">
         <v>5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>130700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16600</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>359600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-181700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-59800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-236300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-40900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-146300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-67000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-52600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-471500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-86500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-483900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>75100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-43300</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>257000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-212500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-190100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-49500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-169200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-104300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-42400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-432200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-83200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-453100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,79 +2175,85 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-5500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>1400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-14100</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-80900</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-95500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-110600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-192200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-35300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-54300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-93100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>68100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-128700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-160500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-97000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-169600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-279700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>426000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,38 +2397,41 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>45300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5900</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-153000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2393,87 +2463,93 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>91400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29600</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>276500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-197800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-382300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-84800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-49000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-262300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>41000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-141300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-264800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-139300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-205800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-362900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>91400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29600</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>276500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-197800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-382300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-84800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-49000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-262300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>41000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-141300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-264800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-139300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-205800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-362900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>349900</v>
+      </c>
+      <c r="E41" s="3">
         <v>302200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>294400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>261200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>247400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>434000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>426900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>668500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>918300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>636400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>337200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1117700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1602100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1277700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1006200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>788400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>703500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>658400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1099500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1361800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1205200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,79 +2976,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114100</v>
+      </c>
+      <c r="E43" s="3">
         <v>127200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>103000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>94800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>94700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>153000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>182100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>173300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>126300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>158900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>141900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>155200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>143600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>112700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>150600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>169300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>145100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>154300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>179300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>212700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2986,8 +3082,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3028,109 +3124,115 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E45" s="3">
         <v>8400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>91700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>67200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>67300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>75400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>61900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>97400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>107100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>86700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>84600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>107900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>113100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>478100</v>
+      </c>
+      <c r="E46" s="3">
         <v>442000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>412800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>382500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>361400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>463700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>723500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>855400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1064700</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3170,221 +3272,233 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2388600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2492300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2540000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2517700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2488800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2476100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1880000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1288900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1227000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1460000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1224700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1594400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1445300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1109100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>905300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>873100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>863100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3032800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3237100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3223500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3766400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3866600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E48" s="3">
         <v>38600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3093400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6614700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6425900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6385200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6815500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6741100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6119700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5470900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5433400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5027300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8252500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9354900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8067900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9218300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10704000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11125800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>532100</v>
+      </c>
+      <c r="E49" s="3">
         <v>538100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>547300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>553300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>560700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>569700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>576900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1197800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1196700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1853500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2506900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2589300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1986900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1949000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2002400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1992000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2153900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2367900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2126800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1417000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1969100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2091700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>176000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>206600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>265400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>257600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3775700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5559100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6782500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4221300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4268900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4549100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>853600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>918200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1076800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3439000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3513300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3542900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3502400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3463800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3562600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6872100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10757100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10743400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11028500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11740800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11877300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11232200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14197800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15443000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15921300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16625300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20200600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19043100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16183500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19160100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19832200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,88 +3922,92 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E57" s="3">
         <v>26300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>45100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>219400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>185900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>188700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>192000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>114700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>121900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>129400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>83200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>109300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>178400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>113100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>132400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>170700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>177900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>9900</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3934,109 +4068,115 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E59" s="3">
         <v>70500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>74800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>84700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>73600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>88000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>847100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>998400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>917300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>528300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>570900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>601800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>516800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>494900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>580800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>318100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>374800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>390000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>511200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>606400</v>
+      </c>
+      <c r="E60" s="3">
         <v>660500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>657000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>663300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>481600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>510400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>428100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>521700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>494000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4076,150 +4216,159 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E61" s="3">
         <v>329900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>340700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>339800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>412600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>420800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3207100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5835400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5782200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5291800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5463100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5679000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5264300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5003200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4714800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4022800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7024000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7938700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7086000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9211100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9453300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9386800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E62" s="3">
         <v>22500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>35900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>111900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>166500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>140400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>134600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>224000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>238900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3090700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3837400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4732900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2059600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3865900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4079400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>457100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>469800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>490400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>974300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1022100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1036600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1039700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>941400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1053400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3846800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6596100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6484200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9367800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10086200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10244000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9841300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12050900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13387100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13812400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14403200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17699100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16457500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13443800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14413600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14616100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4698,16 +4866,16 @@
         <v>794700</v>
       </c>
       <c r="K70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="L70" s="3">
         <v>800300</v>
-      </c>
-      <c r="L70" s="3">
-        <v>800400</v>
       </c>
       <c r="M70" s="3">
         <v>800400</v>
       </c>
       <c r="N70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="O70" s="3">
         <v>854200</v>
@@ -4716,10 +4884,10 @@
         <v>854200</v>
       </c>
       <c r="Q70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="R70" s="3">
         <v>916100</v>
-      </c>
-      <c r="R70" s="3">
-        <v>999500</v>
       </c>
       <c r="S70" s="3">
         <v>999500</v>
@@ -4740,10 +4908,13 @@
         <v>999500</v>
       </c>
       <c r="Y70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="Z70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6840100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6837500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1166100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1163900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1185600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1177800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1023800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1016400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>896100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>647500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>652000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>860300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>854300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>779100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>536600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1292700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1139800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1109500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1222500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1502000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1586100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1740300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3746900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4216600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>91400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29600</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>276500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-197800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-382300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-84800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-49000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-262300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>41000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-141300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-264800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-139300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-205800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-362900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>138700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>135400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-266000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>110800</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>85700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>579300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>145600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>155400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>130900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>138000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>138100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>170100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>190300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>138800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>166400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>273000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>137500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>119400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E89" s="3">
         <v>28700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>35900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27000</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>262600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>120700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>72800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>66800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>76500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>128800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-23900</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>47600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>42300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-59700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5946,16 +6167,16 @@
         <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
@@ -5966,8 +6187,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6008,8 +6229,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-196500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-312400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-259100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>216300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>60900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-322900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>416500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-950100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>114600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>166900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5136600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6263,13 +6497,13 @@
         <v>1700</v>
       </c>
       <c r="G96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H96" s="3">
         <v>1600</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1600</v>
       </c>
       <c r="J96" s="3">
         <v>1600</v>
@@ -6278,11 +6512,11 @@
         <v>1600</v>
       </c>
       <c r="L96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -6308,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-53700</v>
       </c>
       <c r="X96" s="3">
         <v>-53700</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-48500</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>54500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>26800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>923800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>201000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>559300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>213000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>506900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-407900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>99200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1009800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>692700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-329500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E102" s="3">
         <v>7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-98100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-42900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-242600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-212500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-729500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>324600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-778200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-542200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>337300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>254800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>139700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>71400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>63600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-350200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-175100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>108500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>695600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,191 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>43100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>74000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>387000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71900</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>261500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>188500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>694800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>429900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>416600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>257500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>255900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>252200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>237200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>220600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>155400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>123000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>138000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>70200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>552400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,124 +878,130 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>125400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>115500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>93600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>87200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>87500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>83000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>86800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>51700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>42000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>39700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>290700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E10" s="3">
         <v>43100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>74000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>387000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71900</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>261500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>188500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>569400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>314400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>312100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>163900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>168700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>164700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>133800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>103700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>81000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>98300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>50600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>261700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,156 +1180,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>4400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>39600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-40200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-277800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9600</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>133400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1426800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>471900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E15" s="3">
         <v>7200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>8200</v>
       </c>
       <c r="F15" s="3">
         <v>8200</v>
       </c>
       <c r="G15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>44300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>145600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>155400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>128600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>132900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>129200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>138200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>139400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>85600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>80600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>74800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>38100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>110100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E17" s="3">
         <v>44600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>68300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>261400</v>
       </c>
-      <c r="H17" s="3">
-        <v>75500</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="3">
+        <v>75400</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>151800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>741500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>468400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>483400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>501200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>280400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>304100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>308600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>390100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>241100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>188900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>624600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>161900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1036000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>125600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>109700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>64400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-66800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-243700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-51900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-71400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-169500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-85700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-65900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-486600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-91700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-483600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,41 +1545,42 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-45300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5900</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>22300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>153000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1578,123 +1612,129 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E21" s="3">
         <v>5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>57600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>142500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>96700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-165600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>532600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>107100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>88500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-112800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>113500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>86200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>98700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>53100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-213600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-364300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E22" s="3">
         <v>3900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5200</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>130600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15400</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>359700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-180600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-38500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-243700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-51900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-71400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-169500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-85700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-65900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-486600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-91800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-483700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-75200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-23200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-18700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-13200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-15100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>130700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16600</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>359600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-181700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-59800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-64300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-236300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-146300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-67000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-52600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-471500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-86500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-483900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
-        <v>75100</v>
-      </c>
       <c r="H27" s="3">
-        <v>-44300</v>
-      </c>
-      <c r="I27" s="3" t="s">
+        <v>75200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>257000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-212500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-190100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-49500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-169200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-104300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-42400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-36200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-432200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-83200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-453100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,82 +2236,88 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-4200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-5500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>1400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-14100</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-80900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-95500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-110600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-192200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-35300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-54300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-93100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-16400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>68100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-128700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-160500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-97000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-169600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-279700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>426000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,41 +2467,44 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>45300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5900</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-22300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-153000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2466,90 +2536,96 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E33" s="3">
         <v>13800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29600</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>276500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-197800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-382300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-84800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-49000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-262300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-141300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-264800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-139300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-205800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-362900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E35" s="3">
         <v>13800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>91400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29600</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>276500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-197800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-382300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-84800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-49000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-262300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-141300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-264800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-139300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-205800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-362900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>340700</v>
+      </c>
+      <c r="E41" s="3">
         <v>349900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>302200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>294400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>261200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>434000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>426900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>668500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>918300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>636400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>337200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1117700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1602100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1277700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1006200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>788400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>703500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>658400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1099500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1361800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1205200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E43" s="3">
         <v>114100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>103000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>94800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>94700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>153000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>182100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>173300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>126300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>158900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>141900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>155200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>143600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>112700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>94600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>150600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>169300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>145100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>154300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>179300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>212700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3085,8 +3181,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3127,115 +3223,121 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>91700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>67200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>67300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>62400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>75400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>61900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>97400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>107100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>86700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>84600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>107900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>113100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>457200</v>
+      </c>
+      <c r="E46" s="3">
         <v>478100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>442000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>412800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>382500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>361400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>463700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>723500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>855400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1064700</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3275,230 +3377,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2389800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2388600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2492300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2540000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2517700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2488800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2476100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1880000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1288900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1227000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1460000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1224700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1594400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1445300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1109100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>905300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>873100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>863100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3032800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3237100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3223500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3766400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3866600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E48" s="3">
         <v>38200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3093400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6614700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6425900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6385200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6815500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6741100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6119700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5470900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5433400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5027300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8252500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9354900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8067900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9218300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10704000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11125800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>526700</v>
+      </c>
+      <c r="E49" s="3">
         <v>532100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>538100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>547300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>553300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>560700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>569700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>576900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1197800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1196700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1853500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2506900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2589300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1986900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1949000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2002400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1992000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2153900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2367900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2126800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1417000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1969100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2091700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>176000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>206600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>265400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>257600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3775700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5559100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6782500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4221300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4268900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4549100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>853600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>918200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1076800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3408600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3439000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3513300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3542900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3502400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3463800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3562600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6872100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10757100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10743400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11028500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11740800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11877300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11232200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14197800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15443000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15921300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16625300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20200600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19043100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16183500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19160100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19832200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,82 +4053,86 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E57" s="3">
         <v>38700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>219400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>185900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>188700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>192000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>114700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>121900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>129400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>83200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>109300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>178400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>113100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>132400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>170700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>177900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4006,11 +4140,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>9900</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -4071,115 +4205,121 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E59" s="3">
         <v>76600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>70500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>74800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>88000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>847100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>998400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>917300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>528300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>570900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>601800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>516800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>494900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>580800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>318100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>374800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>390000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>511200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>577800</v>
+      </c>
+      <c r="E60" s="3">
         <v>606400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>660500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>657000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>663300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>481600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>510400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>428100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>521700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>494000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4219,156 +4359,165 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>335200</v>
+      </c>
+      <c r="E61" s="3">
         <v>340200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>329900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>340700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>339800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>412600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>420800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3207100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5835400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5782200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5291800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5463100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5679000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5264300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5003200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4714800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4022800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7024000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7938700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7086000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9211100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9453300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9386800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E62" s="3">
         <v>18900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>111900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>166500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>140400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>134600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>224000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>238900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3090700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3837400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4732900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2059600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3865900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4079400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>457100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>469800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>490400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>957800</v>
+      </c>
+      <c r="E66" s="3">
         <v>974300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1022100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1036600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1039700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>941400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1053400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3846800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6596100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6484200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9367800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10086200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10244000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9841300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12050900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13387100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13812400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14403200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17699100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16457500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13443800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14413600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14616100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4869,16 +5037,16 @@
         <v>794700</v>
       </c>
       <c r="L70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="M70" s="3">
         <v>800300</v>
-      </c>
-      <c r="M70" s="3">
-        <v>800400</v>
       </c>
       <c r="N70" s="3">
         <v>800400</v>
       </c>
       <c r="O70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="P70" s="3">
         <v>854200</v>
@@ -4887,10 +5055,10 @@
         <v>854200</v>
       </c>
       <c r="R70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="S70" s="3">
         <v>916100</v>
-      </c>
-      <c r="S70" s="3">
-        <v>999500</v>
       </c>
       <c r="T70" s="3">
         <v>999500</v>
@@ -4911,10 +5079,13 @@
         <v>999500</v>
       </c>
       <c r="Z70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="AA70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6825000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6840100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6837500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1223900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1166100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1163900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1185600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1177800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1023800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1016400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>896100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>647500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>652000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>860300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>854300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>779100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>536600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1292700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1139800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1109500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1222500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1502000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1586100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1740300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3746900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4216600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E81" s="3">
         <v>13800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>91400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29600</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>276500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-197800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-382300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-84800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-49000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-262300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-141300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-264800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-139300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-205800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-362900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>138700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>135400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-266000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>110800</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>85700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>579300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>145600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>155400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>130900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>138000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>138100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>170100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>190300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>138800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>166400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>273000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>137500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>119400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E89" s="3">
         <v>50300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>35900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27000</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>72100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>262600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>120700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>72800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>66800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>76500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>128800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-23900</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>47600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>42300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-59700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,28 +6378,29 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
@@ -6190,8 +6411,8 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E94" s="3">
         <v>17500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-196500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-312400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-259100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>216300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>60900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-322900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>416500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-950100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>114600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>166900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5136600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,13 +6715,14 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E96" s="3">
         <v>1700</v>
@@ -6500,13 +6734,13 @@
         <v>1700</v>
       </c>
       <c r="H96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I96" s="3">
         <v>1600</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1600</v>
       </c>
       <c r="K96" s="3">
         <v>1600</v>
@@ -6515,11 +6749,11 @@
         <v>1600</v>
       </c>
       <c r="M96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -6545,10 +6779,10 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-53700</v>
       </c>
       <c r="Y96" s="3">
         <v>-53700</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-15900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48500</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>54500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>26800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>923800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>201000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>559300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>213000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>506900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-407900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>99200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1009800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>692700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-329500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>47800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-98100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-42900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-242600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-212500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-729500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>324600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-778200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-542200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>337300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>254800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>139700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>71400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>63600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-350200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-175100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>108500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>695600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,205 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3800</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>43100</v>
       </c>
-      <c r="G8" s="3">
-        <v>62200</v>
-      </c>
       <c r="H8" s="3">
+        <v>66200</v>
+      </c>
+      <c r="I8" s="3">
         <v>76100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>392900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>71900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>261500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>188500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>694800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>429900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>416600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>257500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>255900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>252200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>237200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>220600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>123000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>138000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>70200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>552400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -891,130 +897,136 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>125400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>115500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>93600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>87200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>87500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>83000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>86800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>51700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>42000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>290700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>43100</v>
       </c>
-      <c r="G10" s="3">
-        <v>62200</v>
-      </c>
       <c r="H10" s="3">
+        <v>66200</v>
+      </c>
+      <c r="I10" s="3">
         <v>76100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>392900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>261500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>188500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>569400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>314400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>312100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>163900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>168700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>164700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>154200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>133800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>103700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>81000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>98300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>50600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>261700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,168 +1219,177 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-46600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="G14" s="3">
-        <v>39600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-40200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-277800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>10100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>133400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>43300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1426800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>471900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E15" s="3">
         <v>7100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8200</v>
       </c>
       <c r="H15" s="3">
         <v>8200</v>
       </c>
       <c r="I15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>44300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>145600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>155400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>128600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>132900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>129200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>138200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>139400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>85600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>80600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>74800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>38100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>110100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E17" s="3">
         <v>17600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44600</v>
       </c>
-      <c r="G17" s="3">
-        <v>58200</v>
-      </c>
       <c r="H17" s="3">
+        <v>62100</v>
+      </c>
+      <c r="I17" s="3">
         <v>70400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>267200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>75400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>151800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>741500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>468400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>483400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>501200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>280400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>304100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>308600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>390100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>241100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>188900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>624600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>161900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1036000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>125600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>109700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>64400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-46700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-66800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-243700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-51900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-71400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-169500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-85700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-65900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-486600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-91700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-483600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,47 +1612,48 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-45300</v>
-      </c>
       <c r="H20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>22300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>153000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1652,135 +1685,141 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5200</v>
       </c>
-      <c r="G21" s="3">
-        <v>57600</v>
-      </c>
       <c r="H21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I21" s="3">
         <v>19900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>141700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>96700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-165600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>532600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>107100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>88500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-112800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>113500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>86200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>98700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>20800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>53100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>100600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-213600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-364300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>4700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1820,168 +1859,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>130600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>359700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-180600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-243700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-24500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-51900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-71400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-169500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-85700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-65900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-486600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-483700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-75200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-23200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-18700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>130700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>359600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>43000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-181700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-59800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-64300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-236300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-40900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-146300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-67000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-471500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-86500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-483900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E27" s="3">
         <v>16400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-19400</v>
-      </c>
       <c r="H27" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>257000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-212500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-190100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-169200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-27100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-104300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-42400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-432200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-83200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-453100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,88 +2357,94 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>1600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-4200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-5500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-14100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-80900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-95500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-110600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-192200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-54300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-93100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-16400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>68100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-128700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-160500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-97000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-169600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-279700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>426000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,47 +2606,50 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
-        <v>45300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-22300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-153000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2612,96 +2681,102 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E33" s="3">
         <v>31400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>91400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>276500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-197800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-382300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-49000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-262300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>41000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-141300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-264800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-139300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-205800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-362900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E35" s="3">
         <v>31400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>91400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>276500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-197800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-382300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-49000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-262300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>41000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-141300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-264800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-139300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-205800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-362900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3090,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>382500</v>
+      </c>
+      <c r="E41" s="3">
         <v>358400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>340700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>349900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>302200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>294400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>261200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>247400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>345300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>434000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>426900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>668500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>918300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>636400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>337200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1117700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1602100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1277700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1006200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>788400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>703500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>658400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1099500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1361800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1205200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,88 +3254,94 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E43" s="3">
         <v>99100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>103000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>153000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>182100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>173300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>126300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>158900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>141900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>155200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>143600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>112700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>94600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>150600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>169300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>145100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>154300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>179300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>212700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3283,8 +3378,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3325,127 +3420,133 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E45" s="3">
         <v>11500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9800</v>
       </c>
-      <c r="G45" s="3">
-        <v>8400</v>
-      </c>
       <c r="H45" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I45" s="3">
         <v>13200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>91700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>67200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>67300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>62400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>75400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>61900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>97400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>107100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>86700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>84600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>107900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>113100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>607200</v>
+      </c>
+      <c r="E46" s="3">
         <v>474600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>457200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>478100</v>
       </c>
-      <c r="G46" s="3">
-        <v>442000</v>
-      </c>
       <c r="H46" s="3">
+        <v>441400</v>
+      </c>
+      <c r="I46" s="3">
         <v>412800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>382500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>361400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>463700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>723500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>855400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1064700</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3485,248 +3586,260 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2266400</v>
+      </c>
+      <c r="E47" s="3">
         <v>2463500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2389800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2388600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2492300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2540000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2517700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2488800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2476100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1880000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1288900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1227000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1460000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1224700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1594400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1445300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1109100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>905300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>873100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>863100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3032800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3237100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3223500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3766400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3866600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E48" s="3">
         <v>30100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3093400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6614700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6425900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6385200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6815500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6741100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6119700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5470900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5433400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5027300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8252500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9354900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8067900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9218300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10704000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11125800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E49" s="3">
         <v>519900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>526700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>532100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>538100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>547300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>553300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>560700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>569700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>576900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1197800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1196700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1853500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2506900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2589300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1986900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1949000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2002400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1992000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2153900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2367900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2126800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1417000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1969100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2091700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4001,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="G52" s="3">
-        <v>2400</v>
-      </c>
       <c r="H52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>176000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>206600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>265400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>257600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3775700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5559100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6782500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4221300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4268900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4549100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>853600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>918200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1076800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3419200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3490500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3408600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3439000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3513300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3542900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3502400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3463800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3562600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6872100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10757100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10743400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11028500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11740800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11877300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11232200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14197800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15443000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15921300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16625300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20200600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19043100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16183500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19160100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19832200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4314,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E57" s="3">
         <v>36100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38700</v>
       </c>
-      <c r="G57" s="3">
-        <v>26300</v>
-      </c>
       <c r="H57" s="3">
+        <v>26200</v>
+      </c>
+      <c r="I57" s="3">
         <v>20500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>219400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>185900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>188700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>192000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>114700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>121900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>129400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>83200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>109300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>178400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>113100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>132400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>170700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>177900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4280,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4345,127 +4478,133 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E59" s="3">
         <v>93700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>86100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>76600</v>
       </c>
-      <c r="G59" s="3">
-        <v>70500</v>
-      </c>
       <c r="H59" s="3">
+        <v>72200</v>
+      </c>
+      <c r="I59" s="3">
         <v>74800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>73600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>88000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>71800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>847100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>998400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>917300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>528300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>570900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>601800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>516800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>494900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>580800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>318100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>374800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>390000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>511200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>594300</v>
+      </c>
+      <c r="E60" s="3">
         <v>545900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>577800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>606400</v>
       </c>
-      <c r="G60" s="3">
-        <v>660500</v>
-      </c>
       <c r="H60" s="3">
+        <v>650500</v>
+      </c>
+      <c r="I60" s="3">
         <v>657000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>663300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>481600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>510400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>428100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>521700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>494000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4505,168 +4644,177 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E61" s="3">
         <v>362100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>335200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>340200</v>
       </c>
-      <c r="G61" s="3">
-        <v>329900</v>
-      </c>
       <c r="H61" s="3">
+        <v>339700</v>
+      </c>
+      <c r="I61" s="3">
         <v>340700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>339800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>412600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>420800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3207100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5835400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5782200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5291800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5463100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5679000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5264300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5003200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4714800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4022800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7024000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7938700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7086000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9211100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9453300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9386800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E62" s="3">
         <v>34700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18900</v>
       </c>
-      <c r="G62" s="3">
-        <v>22500</v>
-      </c>
       <c r="H62" s="3">
+        <v>22600</v>
+      </c>
+      <c r="I62" s="3">
         <v>28900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>111900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>166500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>140400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>134600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>224000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>238900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3090700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3837400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4732900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2059600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3865900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4079400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>457100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>469800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>490400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>969000</v>
+      </c>
+      <c r="E66" s="3">
         <v>971400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>957800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>974300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1022100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1036600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1039700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>941400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1053400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3846800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6596100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6484200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9367800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10086200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10244000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9841300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12050900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13387100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13812400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14403200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17699100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16457500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13443800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14413600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14616100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5211,16 +5378,16 @@
         <v>794700</v>
       </c>
       <c r="N70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="O70" s="3">
         <v>800300</v>
-      </c>
-      <c r="O70" s="3">
-        <v>800400</v>
       </c>
       <c r="P70" s="3">
         <v>800400</v>
       </c>
       <c r="Q70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="R70" s="3">
         <v>854200</v>
@@ -5229,10 +5396,10 @@
         <v>854200</v>
       </c>
       <c r="T70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="U70" s="3">
         <v>916100</v>
-      </c>
-      <c r="U70" s="3">
-        <v>999500</v>
       </c>
       <c r="V70" s="3">
         <v>999500</v>
@@ -5253,10 +5420,13 @@
         <v>999500</v>
       </c>
       <c r="AB70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="AC70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6761500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6810100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6825000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6840100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6837500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1312600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1257400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1223900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1166100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1163900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1185600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1177800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1023800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1016400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>896100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>647500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>652000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>860300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>854300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>779100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>536600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1292700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1139800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1109500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1222500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1502000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1586100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1740300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3746900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4216600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E81" s="3">
         <v>31400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>91400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>276500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-197800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-382300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-49000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-262300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>41000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-141300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-264800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-139300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-205800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-362900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6022,76 +6220,79 @@
         <v>600</v>
       </c>
       <c r="F83" s="3">
+        <v>600</v>
+      </c>
+      <c r="G83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>119200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>138700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>135400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-266000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>110800</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>85700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>579300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>145600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>155400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>130900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>138000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>138100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>170100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>190300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>138800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>166400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>273000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>137500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>119400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E89" s="3">
         <v>56500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>77000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>35900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>100200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>72100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>262600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>120700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>66800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>76500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>128800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-23900</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>47600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>42300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-59700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,35 +6819,36 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-300</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6638,8 +6858,8 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6680,8 +6900,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-196500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-312400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-259100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>216300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>60900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-322900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>416500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-950100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>114600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>166900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5136600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6962,7 +7195,7 @@
         <v>1800</v>
       </c>
       <c r="F96" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G96" s="3">
         <v>1700</v>
@@ -6974,13 +7207,13 @@
         <v>1700</v>
       </c>
       <c r="J96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K96" s="3">
         <v>1600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>1600</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>1600</v>
@@ -6989,11 +7222,11 @@
         <v>1600</v>
       </c>
       <c r="O96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7019,10 +7252,10 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-53700</v>
       </c>
       <c r="AA96" s="3">
         <v>-53700</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7512,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>54500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>26800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>923800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>201000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>559300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>213000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>506900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-407900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>99200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1009800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>692700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-329500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>2200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>6000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E102" s="3">
         <v>18900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>47800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-98100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-42900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-242600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-212500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-729500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>324600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-778200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-542200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>337300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>254800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>139700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>71400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>63600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-350200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-175100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>108500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>695600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>35300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>DBRG</t>
   </si>
@@ -656,211 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E8" s="3">
         <v>47900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
-        <v>43100</v>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
+        <v>45400</v>
+      </c>
+      <c r="I8" s="3">
         <v>66200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>76100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>392900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>261500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>188500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>694800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>429900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>416600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>257500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>255900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>252200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>237200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>220600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>123000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>138000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>70200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>552400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>359000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -900,133 +907,139 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>125400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>115500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>104500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>93600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>87200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>83000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>86800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>51700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>42000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>39700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>290700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>361500</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E10" s="3">
         <v>47900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-800</v>
       </c>
-      <c r="G10" s="3">
-        <v>43100</v>
-      </c>
       <c r="H10" s="3">
+        <v>45400</v>
+      </c>
+      <c r="I10" s="3">
         <v>66200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>76100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>392900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>261500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>188500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>569400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>314400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>312100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>163900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>168700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>164700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>154200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>133800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>103700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>81000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>98300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>50600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>261700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,174 +1239,183 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-46600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-40200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-277800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>10100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>133400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>16900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>43300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1426800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>471900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>533100</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E15" s="3">
         <v>6500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>8200</v>
       </c>
       <c r="I15" s="3">
         <v>8200</v>
       </c>
       <c r="J15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K15" s="3">
         <v>8100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>44300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>145600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>155400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>128600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>132900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>129200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>138200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>139400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>85600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>80600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>74800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>38100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>110100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>116900</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E17" s="3">
         <v>58900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26000</v>
       </c>
-      <c r="G17" s="3">
-        <v>44600</v>
-      </c>
       <c r="H17" s="3">
+        <v>47000</v>
+      </c>
+      <c r="I17" s="3">
         <v>62100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>267200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>75400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>151800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>741500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>468400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>483400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>501200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>280400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>304100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>308600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>390100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>241100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>188900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>624600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>161900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1036000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>940400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>125600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>109700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>64400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-38500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-66800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-243700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-51900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-71400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-169500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-85700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-65900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-486600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-91700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-483600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,50 +1646,51 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>22300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>153000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1688,141 +1722,147 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>141700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>96700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>72400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-165600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>532600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>107100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>88500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-112800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>113500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>86200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>98700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>20800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>53100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-213600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>45700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-364300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1862,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>32900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>130600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>359700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-180600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-66800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-243700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-51900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-71400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-169500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-85700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-65900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-486600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-483700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-581400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>4900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-75200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-23200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E26" s="3">
         <v>28000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>46900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>130700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>359600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>43000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-181700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-59800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-64300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-236300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-40900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-146300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-471500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-86500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-483900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-591500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>49300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>75300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>257000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-212500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-190100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-49500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-169200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-27100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-104300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-36200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-432200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-83200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-453100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-557200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,91 +2418,97 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>1600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-4200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-5500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-14100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-80900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-95500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-110600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-192200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-35300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-54300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-93100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-16400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>68100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-128700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-160500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-169600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1973400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-279700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>426000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,50 +2676,53 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-22300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-153000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2684,99 +2754,105 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E33" s="3">
         <v>65100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>276500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-197800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-382300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-49000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-262300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-141300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-264800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-139300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-205800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-362900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E35" s="3">
         <v>65100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>276500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-197800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-382300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-49000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-262300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-141300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-264800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-139300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-205800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-362900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,91 +3177,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>411300</v>
+      </c>
+      <c r="E41" s="3">
         <v>382500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>358400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>340700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>349900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>302200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>294400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>261200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>247400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>434000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>426900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>668500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>918300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>636400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>337200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1117700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1602100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1277700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1006200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>788400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>703500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>658400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1099500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1361800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1205200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>455300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3257,91 +3347,97 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E43" s="3">
         <v>200800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>114100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>103000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>153000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>182100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>173300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>126300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>158900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>141900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>155200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>143600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>112700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>94600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>150600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>169300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>145100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>154300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>179300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>212700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3381,8 +3477,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3423,133 +3519,139 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E45" s="3">
         <v>10900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>91700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>67200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>67300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>62400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>75400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>97400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>107100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>86700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>84600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>107900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>113100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>553100</v>
+      </c>
+      <c r="E46" s="3">
         <v>607200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>474600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>457200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>478100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>441400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>412800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>382500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>361400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>463700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>723500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>855400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1064700</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3589,257 +3691,269 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2241500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2266400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2463500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2389800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2388600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2492300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2540000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2517700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2488800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2476100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1880000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1288900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1227000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1460000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1224700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1594400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1445300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1109100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>905300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>873100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>863100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3032800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3237100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3223500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3766400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3866600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3745300</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E48" s="3">
         <v>28200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3093400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6614700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6425900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6385200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6815500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6741100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6119700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5470900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5433400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5027300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8252500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9354900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8067900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9218300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10704000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11125800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9886500</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E49" s="3">
         <v>514000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>519900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>526700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>532100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>538100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>547300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>553300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>560700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>569700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>576900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1197800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1196700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1853500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2506900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2589300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1986900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1949000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2002400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1992000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2153900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2367900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2126800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1417000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1969100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2091700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1813200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,91 +4121,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E52" s="3">
         <v>3300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>176000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>206600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>265400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>257600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3775700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5559100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6782500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4221300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4268900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4549100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>853600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>918200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1076800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5879000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3334000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3419200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3490500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3408600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3439000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3513300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3542900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3502400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3463800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3562600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6872100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10757100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10743400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11028500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11740800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11877300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11232200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14197800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15443000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15921300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16625300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20200600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19043100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16183500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19160100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19832200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22124000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,91 +4445,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E57" s="3">
         <v>43900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>38700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>219400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>185900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>188700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>192000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>114700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>121900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>129400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>83200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>109300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>178400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>113100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>132400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>170700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>177900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4407,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4481,133 +4615,139 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135300</v>
+      </c>
+      <c r="E59" s="3">
         <v>122300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>86100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>76600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>72200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>84700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>73600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>78700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>88000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>847100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>998400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>917300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>528300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>570900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>601800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>516800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>494900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>580800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>318100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>374800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>390000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>511200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>425500</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>594300</v>
+        <v>544000</v>
       </c>
       <c r="E60" s="3">
+        <v>604100</v>
+      </c>
+      <c r="F60" s="3">
         <v>545900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>577800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>606400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>650500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>657000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>663300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>481600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>510400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>428100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>521700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>494000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4647,174 +4787,183 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>331000</v>
+        <v>329200</v>
       </c>
       <c r="E61" s="3">
+        <v>321100</v>
+      </c>
+      <c r="F61" s="3">
         <v>362100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>335200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>340200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>339700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>340700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>339800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>412600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>420800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3207100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5835400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5782200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5291800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5463100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5679000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5264300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5003200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4714800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4022800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7024000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7938700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7086000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9211100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9453300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9386800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8666100</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E62" s="3">
         <v>16800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>27300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>111900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>166500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>140400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>134600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>224000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>238900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3090700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3837400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4732900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2059600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3865900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4079400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>457100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>469800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>490400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>914600</v>
+      </c>
+      <c r="E66" s="3">
         <v>969000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>971400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>957800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>974300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1022100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1036600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1039700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>941400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1053400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3846800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6596100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6484200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9367800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10086200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10244000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9841300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12050900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13387100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13812400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14403200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17699100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16457500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13443800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14413600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14616100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16460300</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5381,16 +5549,16 @@
         <v>794700</v>
       </c>
       <c r="O70" s="3">
+        <v>794700</v>
+      </c>
+      <c r="P70" s="3">
         <v>800300</v>
-      </c>
-      <c r="P70" s="3">
-        <v>800400</v>
       </c>
       <c r="Q70" s="3">
         <v>800400</v>
       </c>
       <c r="R70" s="3">
-        <v>854200</v>
+        <v>800400</v>
       </c>
       <c r="S70" s="3">
         <v>854200</v>
@@ -5399,10 +5567,10 @@
         <v>854200</v>
       </c>
       <c r="U70" s="3">
+        <v>854200</v>
+      </c>
+      <c r="V70" s="3">
         <v>916100</v>
-      </c>
-      <c r="V70" s="3">
-        <v>999500</v>
       </c>
       <c r="W70" s="3">
         <v>999500</v>
@@ -5423,10 +5591,13 @@
         <v>999500</v>
       </c>
       <c r="AC70" s="3">
+        <v>999500</v>
+      </c>
+      <c r="AD70" s="3">
         <v>1407500</v>
       </c>
     </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6758000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6761500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6810100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6825000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6840100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6837500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6816100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6813400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6888500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6842500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6941500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7201700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7176700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6962600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6941700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6875800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6838500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6576200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6557600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6601500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6460300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6195500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6054900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5849100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3806300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3389600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3307900</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1312200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1312600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1257400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1223900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1166100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1163900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1185600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1177800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1023800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1016400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>896100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>647500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>652000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>860300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>854300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>779100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>536600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1292700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1139800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1109500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1222500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1502000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1586100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1740300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3746900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4216600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4256200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E81" s="3">
         <v>65100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>276500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-197800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-382300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-49000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-262300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-141300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-264800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-139300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-205800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2405700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-362900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-555900</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6223,76 +6422,79 @@
         <v>600</v>
       </c>
       <c r="G83" s="3">
+        <v>600</v>
+      </c>
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>119200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>138700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>135400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-266000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>110800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>85700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>579300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>145600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>155400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>130900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>138000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>138100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>170100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>190300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>138800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>166400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>273000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>137500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>119400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>171300</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E89" s="3">
         <v>75600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>77000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>50300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>35900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>100200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>72100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>262600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>120700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>72800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>66800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>76500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>128800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-23900</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>47600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>42300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-59700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-63700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7040,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6829,29 +7050,29 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-300</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3100</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6861,8 +7082,8 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-86000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>17500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-196500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-312400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-259100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1913400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>216300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1043500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1102100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>60900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-322900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>416500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-950100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1096500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>114600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>166900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5136600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-79500</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7198,7 +7432,7 @@
         <v>1800</v>
       </c>
       <c r="G96" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="H96" s="3">
         <v>1700</v>
@@ -7210,13 +7444,13 @@
         <v>1700</v>
       </c>
       <c r="K96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L96" s="3">
         <v>1600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
-        <v>1600</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>1600</v>
@@ -7225,11 +7459,11 @@
         <v>1600</v>
       </c>
       <c r="P96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7255,10 +7489,10 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-106500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-53700</v>
       </c>
       <c r="AB96" s="3">
         <v>-53700</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>-53700</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>-53700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,253 +7758,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>54500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>26800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>923800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>201000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>559300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>213000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>506900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-407900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>99200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1009800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>692700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-329500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4385500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E102" s="3">
         <v>31500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>32600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-98100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-42900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-242600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-212500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-729500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>324600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-778200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-542200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>337300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>254800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>139700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>71400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>63600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-350200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-175100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>108500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>695600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>35300</v>
       </c>
     </row>
